--- a/output/yearly_population_iteration_5_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_5_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6161</v>
+        <v>5644</v>
       </c>
       <c r="C2" t="n">
-        <v>3600</v>
+        <v>6323</v>
       </c>
       <c r="D2" t="n">
-        <v>25568</v>
+        <v>18456</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4214</v>
+        <v>3807</v>
       </c>
       <c r="C3" t="n">
-        <v>4633</v>
+        <v>6848</v>
       </c>
       <c r="D3" t="n">
-        <v>11656</v>
+        <v>13703</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3438</v>
+        <v>3026</v>
       </c>
       <c r="C4" t="n">
-        <v>4390</v>
+        <v>6886</v>
       </c>
       <c r="D4" t="n">
-        <v>5915</v>
+        <v>7315</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1990</v>
+        <v>1765</v>
       </c>
       <c r="C5" t="n">
-        <v>2670</v>
+        <v>5167</v>
       </c>
       <c r="D5" t="n">
-        <v>2598</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1066</v>
+        <v>975</v>
       </c>
       <c r="C6" t="n">
-        <v>1764</v>
+        <v>3293</v>
       </c>
       <c r="D6" t="n">
-        <v>1164</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>523</v>
+        <v>472</v>
       </c>
       <c r="C7" t="n">
-        <v>1291</v>
+        <v>1778</v>
       </c>
       <c r="D7" t="n">
-        <v>677</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="C8" t="n">
-        <v>734</v>
+        <v>759</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="D9" t="n">
         <v>309</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8111</v>
+        <v>7066</v>
       </c>
       <c r="C2" t="n">
-        <v>10999</v>
+        <v>7522</v>
       </c>
       <c r="D2" t="n">
-        <v>34129</v>
+        <v>19753</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4179</v>
+        <v>3764</v>
       </c>
       <c r="C3" t="n">
-        <v>3616</v>
+        <v>5831</v>
       </c>
       <c r="D3" t="n">
-        <v>12857</v>
+        <v>13428</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3249</v>
+        <v>2876</v>
       </c>
       <c r="C4" t="n">
-        <v>4422</v>
+        <v>6658</v>
       </c>
       <c r="D4" t="n">
-        <v>6727</v>
+        <v>8135</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2344</v>
+        <v>2042</v>
       </c>
       <c r="C5" t="n">
-        <v>3430</v>
+        <v>5851</v>
       </c>
       <c r="D5" t="n">
-        <v>3035</v>
+        <v>3416</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1344</v>
+        <v>1187</v>
       </c>
       <c r="C6" t="n">
-        <v>2180</v>
+        <v>4056</v>
       </c>
       <c r="D6" t="n">
-        <v>1382</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>688</v>
+        <v>612</v>
       </c>
       <c r="C7" t="n">
-        <v>1500</v>
+        <v>2445</v>
       </c>
       <c r="D7" t="n">
-        <v>739</v>
+        <v>723</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>307</v>
+        <v>262</v>
       </c>
       <c r="C8" t="n">
-        <v>990</v>
+        <v>1180</v>
       </c>
       <c r="D8" t="n">
-        <v>469</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C9" t="n">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
         <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11785</v>
+        <v>7492</v>
       </c>
       <c r="C2" t="n">
-        <v>8934</v>
+        <v>8633</v>
       </c>
       <c r="D2" t="n">
-        <v>46148</v>
+        <v>24201</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4761</v>
+        <v>4111</v>
       </c>
       <c r="C3" t="n">
-        <v>6082</v>
+        <v>5786</v>
       </c>
       <c r="D3" t="n">
-        <v>14886</v>
+        <v>13327</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3148</v>
+        <v>2754</v>
       </c>
       <c r="C4" t="n">
-        <v>3950</v>
+        <v>6098</v>
       </c>
       <c r="D4" t="n">
-        <v>7522</v>
+        <v>8571</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2422</v>
+        <v>2108</v>
       </c>
       <c r="C5" t="n">
-        <v>3773</v>
+        <v>6070</v>
       </c>
       <c r="D5" t="n">
-        <v>3480</v>
+        <v>3991</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1605</v>
+        <v>1384</v>
       </c>
       <c r="C6" t="n">
-        <v>2711</v>
+        <v>4704</v>
       </c>
       <c r="D6" t="n">
-        <v>1617</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>872</v>
+        <v>751</v>
       </c>
       <c r="C7" t="n">
-        <v>1777</v>
+        <v>3067</v>
       </c>
       <c r="D7" t="n">
-        <v>818</v>
+        <v>810</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>409</v>
+        <v>353</v>
       </c>
       <c r="C8" t="n">
-        <v>1204</v>
+        <v>1675</v>
       </c>
       <c r="D8" t="n">
-        <v>503</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="C9" t="n">
-        <v>705</v>
+        <v>751</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>373</v>
+        <v>345</v>
       </c>
       <c r="D10" t="n">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10373</v>
+        <v>6913</v>
       </c>
       <c r="C2" t="n">
-        <v>5860</v>
+        <v>5939</v>
       </c>
       <c r="D2" t="n">
-        <v>36977</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5805</v>
+        <v>4938</v>
       </c>
       <c r="C3" t="n">
-        <v>8642</v>
+        <v>9038</v>
       </c>
       <c r="D3" t="n">
-        <v>16469</v>
+        <v>14787</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2237</v>
+        <v>1947</v>
       </c>
       <c r="C4" t="n">
-        <v>5897</v>
+        <v>9164</v>
       </c>
       <c r="D4" t="n">
-        <v>7354</v>
+        <v>8353</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1483</v>
+        <v>1278</v>
       </c>
       <c r="C5" t="n">
-        <v>2656</v>
+        <v>4609</v>
       </c>
       <c r="D5" t="n">
-        <v>2553</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>805</v>
+        <v>693</v>
       </c>
       <c r="C6" t="n">
-        <v>1741</v>
+        <v>3005</v>
       </c>
       <c r="D6" t="n">
-        <v>801</v>
+        <v>793</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>326</v>
       </c>
       <c r="C7" t="n">
-        <v>1179</v>
+        <v>1641</v>
       </c>
       <c r="D7" t="n">
-        <v>492</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>690</v>
+        <v>735</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>365</v>
+        <v>338</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="D10" t="n">
         <v>201</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6024</v>
+        <v>4324</v>
       </c>
       <c r="C2" t="n">
-        <v>2362</v>
+        <v>2812</v>
       </c>
       <c r="D2" t="n">
-        <v>25846</v>
+        <v>14503</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6650</v>
+        <v>4988</v>
       </c>
       <c r="C3" t="n">
-        <v>6596</v>
+        <v>6934</v>
       </c>
       <c r="D3" t="n">
-        <v>18605</v>
+        <v>14644</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3171</v>
+        <v>2674</v>
       </c>
       <c r="C4" t="n">
-        <v>7344</v>
+        <v>9179</v>
       </c>
       <c r="D4" t="n">
-        <v>8601</v>
+        <v>9247</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1679</v>
+        <v>1442</v>
       </c>
       <c r="C5" t="n">
-        <v>4128</v>
+        <v>6614</v>
       </c>
       <c r="D5" t="n">
-        <v>3169</v>
+        <v>3369</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>984</v>
+        <v>826</v>
       </c>
       <c r="C6" t="n">
-        <v>2163</v>
+        <v>3742</v>
       </c>
       <c r="D6" t="n">
-        <v>1007</v>
+        <v>989</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>358</v>
+        <v>308</v>
       </c>
       <c r="C7" t="n">
-        <v>1447</v>
+        <v>2129</v>
       </c>
       <c r="D7" t="n">
-        <v>534</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>883</v>
+        <v>998</v>
       </c>
       <c r="D8" t="n">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>424</v>
+        <v>380</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6310</v>
+        <v>4427</v>
       </c>
       <c r="C2" t="n">
-        <v>6959</v>
+        <v>7919</v>
       </c>
       <c r="D2" t="n">
-        <v>22511</v>
+        <v>23536</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5398</v>
+        <v>3994</v>
       </c>
       <c r="C3" t="n">
-        <v>3933</v>
+        <v>4431</v>
       </c>
       <c r="D3" t="n">
-        <v>18367</v>
+        <v>13640</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4030</v>
+        <v>3132</v>
       </c>
       <c r="C4" t="n">
-        <v>6873</v>
+        <v>7888</v>
       </c>
       <c r="D4" t="n">
-        <v>10068</v>
+        <v>9846</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2069</v>
+        <v>1741</v>
       </c>
       <c r="C5" t="n">
-        <v>5616</v>
+        <v>7746</v>
       </c>
       <c r="D5" t="n">
-        <v>3959</v>
+        <v>4169</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1189</v>
+        <v>998</v>
       </c>
       <c r="C6" t="n">
-        <v>3086</v>
+        <v>4974</v>
       </c>
       <c r="D6" t="n">
-        <v>1325</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>537</v>
+        <v>446</v>
       </c>
       <c r="C7" t="n">
-        <v>1783</v>
+        <v>2844</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C8" t="n">
-        <v>1128</v>
+        <v>1461</v>
       </c>
       <c r="D8" t="n">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="D9" t="n">
-        <v>275</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="D10" t="n">
         <v>213</v>
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3665</v>
+        <v>2630</v>
       </c>
       <c r="C2" t="n">
-        <v>3077</v>
+        <v>3715</v>
       </c>
       <c r="D2" t="n">
-        <v>15584</v>
+        <v>16441</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5428</v>
+        <v>3987</v>
       </c>
       <c r="C3" t="n">
-        <v>4883</v>
+        <v>5468</v>
       </c>
       <c r="D3" t="n">
-        <v>18390</v>
+        <v>14363</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4513</v>
+        <v>3432</v>
       </c>
       <c r="C4" t="n">
-        <v>6411</v>
+        <v>7352</v>
       </c>
       <c r="D4" t="n">
-        <v>11041</v>
+        <v>10387</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2160</v>
+        <v>1803</v>
       </c>
       <c r="C5" t="n">
-        <v>6634</v>
+        <v>9022</v>
       </c>
       <c r="D5" t="n">
-        <v>4317</v>
+        <v>4387</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1001</v>
+        <v>817</v>
       </c>
       <c r="C6" t="n">
-        <v>3889</v>
+        <v>5873</v>
       </c>
       <c r="D6" t="n">
-        <v>1309</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>1963</v>
+        <v>2855</v>
       </c>
       <c r="D7" t="n">
-        <v>599</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>959</v>
+        <v>1044</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5200</v>
+        <v>3501</v>
       </c>
       <c r="C2" t="n">
-        <v>3443</v>
+        <v>5184</v>
       </c>
       <c r="D2" t="n">
-        <v>17091</v>
+        <v>18199</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3989</v>
+        <v>2934</v>
       </c>
       <c r="C3" t="n">
-        <v>3530</v>
+        <v>4163</v>
       </c>
       <c r="D3" t="n">
-        <v>16897</v>
+        <v>13818</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4280</v>
+        <v>3225</v>
       </c>
       <c r="C4" t="n">
-        <v>5576</v>
+        <v>6383</v>
       </c>
       <c r="D4" t="n">
-        <v>11904</v>
+        <v>10681</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2798</v>
+        <v>2172</v>
       </c>
       <c r="C5" t="n">
-        <v>6454</v>
+        <v>8096</v>
       </c>
       <c r="D5" t="n">
-        <v>5218</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1315</v>
+        <v>1067</v>
       </c>
       <c r="C6" t="n">
-        <v>5101</v>
+        <v>7264</v>
       </c>
       <c r="D6" t="n">
-        <v>1724</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>392</v>
+        <v>309</v>
       </c>
       <c r="C7" t="n">
-        <v>2812</v>
+        <v>4064</v>
       </c>
       <c r="D7" t="n">
-        <v>696</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>1361</v>
+        <v>1730</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>45</v>
+      </c>
+      <c r="D14" t="n">
         <v>47</v>
-      </c>
-      <c r="D14" t="n">
-        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3640</v>
+        <v>2361</v>
       </c>
       <c r="C2" t="n">
-        <v>2145</v>
+        <v>3723</v>
       </c>
       <c r="D2" t="n">
-        <v>13241</v>
+        <v>13046</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3850</v>
+        <v>2730</v>
       </c>
       <c r="C3" t="n">
-        <v>3192</v>
+        <v>4142</v>
       </c>
       <c r="D3" t="n">
-        <v>16137</v>
+        <v>13724</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3858</v>
+        <v>2893</v>
       </c>
       <c r="C4" t="n">
-        <v>4702</v>
+        <v>5538</v>
       </c>
       <c r="D4" t="n">
-        <v>12327</v>
+        <v>10850</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3072</v>
+        <v>2370</v>
       </c>
       <c r="C5" t="n">
-        <v>6230</v>
+        <v>7630</v>
       </c>
       <c r="D5" t="n">
-        <v>5879</v>
+        <v>5598</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1600</v>
+        <v>1249</v>
       </c>
       <c r="C6" t="n">
-        <v>5755</v>
+        <v>7819</v>
       </c>
       <c r="D6" t="n">
-        <v>2089</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>383</v>
+        <v>279</v>
       </c>
       <c r="C7" t="n">
-        <v>3609</v>
+        <v>5053</v>
       </c>
       <c r="D7" t="n">
-        <v>777</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1752</v>
+        <v>2290</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>646</v>
+        <v>598</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6919</v>
+        <v>3807</v>
       </c>
       <c r="C2" t="n">
-        <v>9429</v>
+        <v>14860</v>
       </c>
       <c r="D2" t="n">
-        <v>13061</v>
+        <v>12671</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3169</v>
+        <v>2191</v>
       </c>
       <c r="C3" t="n">
-        <v>2461</v>
+        <v>3537</v>
       </c>
       <c r="D3" t="n">
-        <v>14707</v>
+        <v>12764</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3383</v>
+        <v>2465</v>
       </c>
       <c r="C4" t="n">
-        <v>3937</v>
+        <v>4833</v>
       </c>
       <c r="D4" t="n">
-        <v>12537</v>
+        <v>10934</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3052</v>
+        <v>2324</v>
       </c>
       <c r="C5" t="n">
-        <v>5454</v>
+        <v>6627</v>
       </c>
       <c r="D5" t="n">
-        <v>6628</v>
+        <v>6133</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1971</v>
+        <v>1509</v>
       </c>
       <c r="C6" t="n">
-        <v>5895</v>
+        <v>7680</v>
       </c>
       <c r="D6" t="n">
-        <v>2571</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>701</v>
+        <v>516</v>
       </c>
       <c r="C7" t="n">
-        <v>4448</v>
+        <v>6130</v>
       </c>
       <c r="D7" t="n">
-        <v>936</v>
+        <v>884</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>2460</v>
+        <v>3236</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1031</v>
+        <v>1150</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>369</v>
+        <v>335</v>
       </c>
       <c r="D10" t="n">
-        <v>195</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6162</v>
+        <v>5535</v>
       </c>
       <c r="C2" t="n">
-        <v>6159</v>
+        <v>5229</v>
       </c>
       <c r="D2" t="n">
-        <v>13171</v>
+        <v>11808</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4839</v>
+        <v>2753</v>
       </c>
       <c r="C2" t="n">
-        <v>5205</v>
+        <v>8559</v>
       </c>
       <c r="D2" t="n">
-        <v>9612</v>
+        <v>9427</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4457</v>
+        <v>2969</v>
       </c>
       <c r="C3" t="n">
-        <v>4393</v>
+        <v>6384</v>
       </c>
       <c r="D3" t="n">
-        <v>15676</v>
+        <v>13697</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4551</v>
+        <v>3406</v>
       </c>
       <c r="C4" t="n">
-        <v>5657</v>
+        <v>7078</v>
       </c>
       <c r="D4" t="n">
-        <v>12840</v>
+        <v>11233</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1934</v>
+        <v>1437</v>
       </c>
       <c r="C5" t="n">
-        <v>8171</v>
+        <v>10358</v>
       </c>
       <c r="D5" t="n">
-        <v>6095</v>
+        <v>5608</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>647</v>
+        <v>476</v>
       </c>
       <c r="C6" t="n">
-        <v>5630</v>
+        <v>7437</v>
       </c>
       <c r="D6" t="n">
-        <v>2048</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>2410</v>
+        <v>3171</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1010</v>
+        <v>1127</v>
       </c>
       <c r="D8" t="n">
-        <v>302</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>361</v>
+        <v>328</v>
       </c>
       <c r="D9" t="n">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6992</v>
+        <v>6831</v>
       </c>
       <c r="C2" t="n">
-        <v>4316</v>
+        <v>5198</v>
       </c>
       <c r="D2" t="n">
-        <v>15216</v>
+        <v>14525</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2618</v>
+        <v>2352</v>
       </c>
       <c r="C3" t="n">
-        <v>3104</v>
+        <v>2635</v>
       </c>
       <c r="D3" t="n">
-        <v>2852</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="4">
@@ -4554,7 +4554,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
         <v>381</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4542</v>
+        <v>4496</v>
       </c>
       <c r="C2" t="n">
-        <v>2785</v>
+        <v>9403</v>
       </c>
       <c r="D2" t="n">
-        <v>17244</v>
+        <v>25341</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3945</v>
+        <v>3768</v>
       </c>
       <c r="C3" t="n">
-        <v>3268</v>
+        <v>3564</v>
       </c>
       <c r="D3" t="n">
-        <v>4719</v>
+        <v>4429</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1171</v>
+        <v>1055</v>
       </c>
       <c r="C4" t="n">
-        <v>1862</v>
+        <v>1587</v>
       </c>
       <c r="D4" t="n">
-        <v>1756</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="5">
@@ -4865,7 +4865,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
         <v>221</v>
@@ -4885,7 +4885,7 @@
         <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4588</v>
+        <v>4571</v>
       </c>
       <c r="C2" t="n">
-        <v>2701</v>
+        <v>6605</v>
       </c>
       <c r="D2" t="n">
-        <v>20396</v>
+        <v>23574</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3494</v>
+        <v>3399</v>
       </c>
       <c r="C3" t="n">
-        <v>2600</v>
+        <v>5841</v>
       </c>
       <c r="D3" t="n">
-        <v>6383</v>
+        <v>7456</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2165</v>
+        <v>2040</v>
       </c>
       <c r="C4" t="n">
-        <v>2619</v>
+        <v>2673</v>
       </c>
       <c r="D4" t="n">
-        <v>2271</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>541</v>
+        <v>493</v>
       </c>
       <c r="C5" t="n">
-        <v>1112</v>
+        <v>963</v>
       </c>
       <c r="D5" t="n">
-        <v>1242</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5608</v>
+        <v>5351</v>
       </c>
       <c r="C2" t="n">
-        <v>3583</v>
+        <v>9153</v>
       </c>
       <c r="D2" t="n">
-        <v>15897</v>
+        <v>24182</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3302</v>
+        <v>3253</v>
       </c>
       <c r="C3" t="n">
-        <v>2304</v>
+        <v>5426</v>
       </c>
       <c r="D3" t="n">
-        <v>8063</v>
+        <v>9381</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2395</v>
+        <v>2317</v>
       </c>
       <c r="C4" t="n">
-        <v>2554</v>
+        <v>4294</v>
       </c>
       <c r="D4" t="n">
-        <v>2930</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1128</v>
+        <v>1037</v>
       </c>
       <c r="C5" t="n">
-        <v>1884</v>
+        <v>1845</v>
       </c>
       <c r="D5" t="n">
-        <v>1391</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="C6" t="n">
-        <v>708</v>
+        <v>634</v>
       </c>
       <c r="D6" t="n">
-        <v>958</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
         <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5574,10 +5574,10 @@
         <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>178</v>
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8671</v>
+        <v>7106</v>
       </c>
       <c r="C2" t="n">
-        <v>6726</v>
+        <v>10734</v>
       </c>
       <c r="D2" t="n">
-        <v>20468</v>
+        <v>31468</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3231</v>
+        <v>3102</v>
       </c>
       <c r="C3" t="n">
-        <v>2431</v>
+        <v>6005</v>
       </c>
       <c r="D3" t="n">
-        <v>8172</v>
+        <v>10321</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1767</v>
+        <v>1718</v>
       </c>
       <c r="C4" t="n">
-        <v>1979</v>
+        <v>3996</v>
       </c>
       <c r="D4" t="n">
-        <v>3270</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>934</v>
+        <v>879</v>
       </c>
       <c r="C5" t="n">
-        <v>1620</v>
+        <v>2298</v>
       </c>
       <c r="D5" t="n">
-        <v>1321</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="C6" t="n">
-        <v>884</v>
+        <v>838</v>
       </c>
       <c r="D6" t="n">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6846</v>
+        <v>6593</v>
       </c>
       <c r="C2" t="n">
-        <v>7633</v>
+        <v>9826</v>
       </c>
       <c r="D2" t="n">
-        <v>17475</v>
+        <v>23378</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5012</v>
+        <v>4255</v>
       </c>
       <c r="C3" t="n">
-        <v>4314</v>
+        <v>7542</v>
       </c>
       <c r="D3" t="n">
-        <v>9721</v>
+        <v>13114</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2194</v>
+        <v>2117</v>
       </c>
       <c r="C4" t="n">
-        <v>2219</v>
+        <v>5127</v>
       </c>
       <c r="D4" t="n">
-        <v>4205</v>
+        <v>4814</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1220</v>
+        <v>1160</v>
       </c>
       <c r="C5" t="n">
-        <v>1803</v>
+        <v>3244</v>
       </c>
       <c r="D5" t="n">
-        <v>1661</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>599</v>
+        <v>545</v>
       </c>
       <c r="C6" t="n">
-        <v>1303</v>
+        <v>1646</v>
       </c>
       <c r="D6" t="n">
-        <v>876</v>
+        <v>863</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="C7" t="n">
-        <v>653</v>
+        <v>610</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,7 +6179,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
         <v>174</v>
@@ -6199,7 +6199,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5338</v>
+        <v>4806</v>
       </c>
       <c r="C2" t="n">
-        <v>5328</v>
+        <v>8078</v>
       </c>
       <c r="D2" t="n">
-        <v>23951</v>
+        <v>19661</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4885</v>
+        <v>4433</v>
       </c>
       <c r="C3" t="n">
-        <v>5340</v>
+        <v>7606</v>
       </c>
       <c r="D3" t="n">
-        <v>10308</v>
+        <v>13812</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3131</v>
+        <v>2732</v>
       </c>
       <c r="C4" t="n">
-        <v>3399</v>
+        <v>6388</v>
       </c>
       <c r="D4" t="n">
-        <v>5189</v>
+        <v>6261</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1502</v>
+        <v>1426</v>
       </c>
       <c r="C5" t="n">
-        <v>1983</v>
+        <v>4206</v>
       </c>
       <c r="D5" t="n">
-        <v>2098</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>839</v>
+        <v>775</v>
       </c>
       <c r="C6" t="n">
-        <v>1565</v>
+        <v>2470</v>
       </c>
       <c r="D6" t="n">
-        <v>998</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>355</v>
+        <v>317</v>
       </c>
       <c r="C7" t="n">
-        <v>1009</v>
+        <v>1141</v>
       </c>
       <c r="D7" t="n">
-        <v>617</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>480</v>
+        <v>443</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_5_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_5_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5644</v>
+        <v>7188</v>
       </c>
       <c r="C2" t="n">
-        <v>6323</v>
+        <v>9716</v>
       </c>
       <c r="D2" t="n">
-        <v>18456</v>
+        <v>37610</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3807</v>
+        <v>4195</v>
       </c>
       <c r="C3" t="n">
-        <v>6848</v>
+        <v>5081</v>
       </c>
       <c r="D3" t="n">
-        <v>13703</v>
+        <v>21078</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3026</v>
+        <v>3042</v>
       </c>
       <c r="C4" t="n">
-        <v>6886</v>
+        <v>5129</v>
       </c>
       <c r="D4" t="n">
-        <v>7315</v>
+        <v>8047</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1765</v>
+        <v>1918</v>
       </c>
       <c r="C5" t="n">
-        <v>5167</v>
+        <v>4909</v>
       </c>
       <c r="D5" t="n">
-        <v>2844</v>
+        <v>2659</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>975</v>
+        <v>1048</v>
       </c>
       <c r="C6" t="n">
-        <v>3293</v>
+        <v>3360</v>
       </c>
       <c r="D6" t="n">
-        <v>1179</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C7" t="n">
-        <v>1778</v>
+        <v>1768</v>
       </c>
       <c r="D7" t="n">
-        <v>661</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C8" t="n">
-        <v>759</v>
+        <v>777</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
         <v>161</v>
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7066</v>
+        <v>8758</v>
       </c>
       <c r="C2" t="n">
-        <v>7522</v>
+        <v>5889</v>
       </c>
       <c r="D2" t="n">
-        <v>19753</v>
+        <v>30774</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3764</v>
+        <v>4502</v>
       </c>
       <c r="C3" t="n">
-        <v>5831</v>
+        <v>6296</v>
       </c>
       <c r="D3" t="n">
-        <v>13428</v>
+        <v>21909</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2876</v>
+        <v>3010</v>
       </c>
       <c r="C4" t="n">
-        <v>6658</v>
+        <v>4999</v>
       </c>
       <c r="D4" t="n">
-        <v>8135</v>
+        <v>9929</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2042</v>
+        <v>2109</v>
       </c>
       <c r="C5" t="n">
-        <v>5851</v>
+        <v>4859</v>
       </c>
       <c r="D5" t="n">
-        <v>3416</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1187</v>
+        <v>1283</v>
       </c>
       <c r="C6" t="n">
-        <v>4056</v>
+        <v>4011</v>
       </c>
       <c r="D6" t="n">
-        <v>1418</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>612</v>
+        <v>645</v>
       </c>
       <c r="C7" t="n">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="D7" t="n">
-        <v>723</v>
+        <v>691</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C8" t="n">
-        <v>1180</v>
+        <v>1194</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7492</v>
+        <v>8887</v>
       </c>
       <c r="C2" t="n">
-        <v>8633</v>
+        <v>7742</v>
       </c>
       <c r="D2" t="n">
-        <v>24201</v>
+        <v>33889</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4111</v>
+        <v>5008</v>
       </c>
       <c r="C3" t="n">
-        <v>5786</v>
+        <v>5457</v>
       </c>
       <c r="D3" t="n">
-        <v>13327</v>
+        <v>21570</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2754</v>
+        <v>3060</v>
       </c>
       <c r="C4" t="n">
-        <v>6098</v>
+        <v>5394</v>
       </c>
       <c r="D4" t="n">
-        <v>8571</v>
+        <v>11256</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2108</v>
+        <v>2209</v>
       </c>
       <c r="C5" t="n">
-        <v>6070</v>
+        <v>4769</v>
       </c>
       <c r="D5" t="n">
-        <v>3991</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1384</v>
+        <v>1456</v>
       </c>
       <c r="C6" t="n">
-        <v>4704</v>
+        <v>4317</v>
       </c>
       <c r="D6" t="n">
-        <v>1654</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>751</v>
+        <v>796</v>
       </c>
       <c r="C7" t="n">
-        <v>3067</v>
+        <v>3028</v>
       </c>
       <c r="D7" t="n">
-        <v>810</v>
+        <v>771</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="C8" t="n">
-        <v>1675</v>
+        <v>1656</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9">
@@ -1503,10 +1503,10 @@
         <v>139</v>
       </c>
       <c r="C9" t="n">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6913</v>
+        <v>8270</v>
       </c>
       <c r="C2" t="n">
-        <v>5939</v>
+        <v>5326</v>
       </c>
       <c r="D2" t="n">
-        <v>20000</v>
+        <v>28146</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4938</v>
+        <v>5721</v>
       </c>
       <c r="C3" t="n">
-        <v>9038</v>
+        <v>8384</v>
       </c>
       <c r="D3" t="n">
-        <v>14787</v>
+        <v>23129</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1947</v>
+        <v>2041</v>
       </c>
       <c r="C4" t="n">
-        <v>9164</v>
+        <v>7478</v>
       </c>
       <c r="D4" t="n">
-        <v>8353</v>
+        <v>10264</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1278</v>
+        <v>1345</v>
       </c>
       <c r="C5" t="n">
-        <v>4609</v>
+        <v>4230</v>
       </c>
       <c r="D5" t="n">
-        <v>2693</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>693</v>
+        <v>735</v>
       </c>
       <c r="C6" t="n">
-        <v>3005</v>
+        <v>2967</v>
       </c>
       <c r="D6" t="n">
-        <v>793</v>
+        <v>755</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C7" t="n">
-        <v>1641</v>
+        <v>1622</v>
       </c>
       <c r="D7" t="n">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8">
@@ -1800,10 +1800,10 @@
         <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>735</v>
+        <v>750</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>37</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4324</v>
+        <v>5017</v>
       </c>
       <c r="C2" t="n">
-        <v>2812</v>
+        <v>2486</v>
       </c>
       <c r="D2" t="n">
-        <v>14503</v>
+        <v>20110</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4988</v>
+        <v>5846</v>
       </c>
       <c r="C3" t="n">
-        <v>6934</v>
+        <v>6396</v>
       </c>
       <c r="D3" t="n">
-        <v>14644</v>
+        <v>22701</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2674</v>
+        <v>2930</v>
       </c>
       <c r="C4" t="n">
-        <v>9179</v>
+        <v>7946</v>
       </c>
       <c r="D4" t="n">
-        <v>9247</v>
+        <v>11903</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1442</v>
+        <v>1498</v>
       </c>
       <c r="C5" t="n">
-        <v>6614</v>
+        <v>5654</v>
       </c>
       <c r="D5" t="n">
-        <v>3369</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>826</v>
+        <v>877</v>
       </c>
       <c r="C6" t="n">
-        <v>3742</v>
+        <v>3543</v>
       </c>
       <c r="D6" t="n">
-        <v>989</v>
+        <v>933</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C7" t="n">
-        <v>2129</v>
+        <v>2120</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8">
@@ -2111,10 +2111,10 @@
         <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
         <v>211</v>
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2184,7 +2184,7 @@
         <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4427</v>
+        <v>5538</v>
       </c>
       <c r="C2" t="n">
-        <v>7919</v>
+        <v>5699</v>
       </c>
       <c r="D2" t="n">
-        <v>23536</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3994</v>
+        <v>4624</v>
       </c>
       <c r="C3" t="n">
-        <v>4431</v>
+        <v>4084</v>
       </c>
       <c r="D3" t="n">
-        <v>13640</v>
+        <v>20823</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3132</v>
+        <v>3589</v>
       </c>
       <c r="C4" t="n">
-        <v>7888</v>
+        <v>7036</v>
       </c>
       <c r="D4" t="n">
-        <v>9846</v>
+        <v>13303</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1741</v>
+        <v>1848</v>
       </c>
       <c r="C5" t="n">
-        <v>7746</v>
+        <v>6592</v>
       </c>
       <c r="D5" t="n">
-        <v>4169</v>
+        <v>4778</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>998</v>
+        <v>1035</v>
       </c>
       <c r="C6" t="n">
-        <v>4974</v>
+        <v>4475</v>
       </c>
       <c r="D6" t="n">
-        <v>1318</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="C7" t="n">
-        <v>2844</v>
+        <v>2739</v>
       </c>
       <c r="D7" t="n">
-        <v>576</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C8" t="n">
-        <v>1461</v>
+        <v>1444</v>
       </c>
       <c r="D8" t="n">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D10" t="n">
         <v>213</v>
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2495,7 +2495,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2630</v>
+        <v>3316</v>
       </c>
       <c r="C2" t="n">
-        <v>3715</v>
+        <v>2709</v>
       </c>
       <c r="D2" t="n">
-        <v>16441</v>
+        <v>15045</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3987</v>
+        <v>4668</v>
       </c>
       <c r="C3" t="n">
-        <v>5468</v>
+        <v>4496</v>
       </c>
       <c r="D3" t="n">
-        <v>14363</v>
+        <v>20437</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3432</v>
+        <v>3928</v>
       </c>
       <c r="C4" t="n">
-        <v>7352</v>
+        <v>6629</v>
       </c>
       <c r="D4" t="n">
-        <v>10387</v>
+        <v>14232</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1803</v>
+        <v>1894</v>
       </c>
       <c r="C5" t="n">
-        <v>9022</v>
+        <v>7693</v>
       </c>
       <c r="D5" t="n">
-        <v>4387</v>
+        <v>5065</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>817</v>
+        <v>839</v>
       </c>
       <c r="C6" t="n">
-        <v>5873</v>
+        <v>5324</v>
       </c>
       <c r="D6" t="n">
-        <v>1290</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>2855</v>
+        <v>2789</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1044</v>
+        <v>1022</v>
       </c>
       <c r="D8" t="n">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2747,7 +2747,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
         <v>286</v>
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2792,7 +2792,7 @@
         <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3501</v>
+        <v>4255</v>
       </c>
       <c r="C2" t="n">
-        <v>5184</v>
+        <v>3916</v>
       </c>
       <c r="D2" t="n">
-        <v>18199</v>
+        <v>13520</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2934</v>
+        <v>3526</v>
       </c>
       <c r="C3" t="n">
-        <v>4163</v>
+        <v>3306</v>
       </c>
       <c r="D3" t="n">
-        <v>13818</v>
+        <v>18526</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3225</v>
+        <v>3686</v>
       </c>
       <c r="C4" t="n">
-        <v>6383</v>
+        <v>5508</v>
       </c>
       <c r="D4" t="n">
-        <v>10681</v>
+        <v>14752</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2172</v>
+        <v>2378</v>
       </c>
       <c r="C5" t="n">
-        <v>8096</v>
+        <v>7136</v>
       </c>
       <c r="D5" t="n">
-        <v>5117</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1067</v>
+        <v>1116</v>
       </c>
       <c r="C6" t="n">
-        <v>7264</v>
+        <v>6306</v>
       </c>
       <c r="D6" t="n">
-        <v>1689</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C7" t="n">
-        <v>4064</v>
+        <v>3836</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>1730</v>
+        <v>1665</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2361</v>
+        <v>2905</v>
       </c>
       <c r="C2" t="n">
-        <v>3723</v>
+        <v>2208</v>
       </c>
       <c r="D2" t="n">
-        <v>13046</v>
+        <v>10198</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2730</v>
+        <v>3294</v>
       </c>
       <c r="C3" t="n">
-        <v>4142</v>
+        <v>3219</v>
       </c>
       <c r="D3" t="n">
-        <v>13724</v>
+        <v>17095</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2893</v>
+        <v>3350</v>
       </c>
       <c r="C4" t="n">
-        <v>5538</v>
+        <v>4664</v>
       </c>
       <c r="D4" t="n">
-        <v>10850</v>
+        <v>14916</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2370</v>
+        <v>2624</v>
       </c>
       <c r="C5" t="n">
-        <v>7630</v>
+        <v>6683</v>
       </c>
       <c r="D5" t="n">
-        <v>5598</v>
+        <v>7001</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1249</v>
+        <v>1320</v>
       </c>
       <c r="C6" t="n">
-        <v>7819</v>
+        <v>6820</v>
       </c>
       <c r="D6" t="n">
-        <v>2014</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C7" t="n">
-        <v>5053</v>
+        <v>4678</v>
       </c>
       <c r="D7" t="n">
-        <v>742</v>
+        <v>732</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>2290</v>
+        <v>2155</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3807</v>
+        <v>5086</v>
       </c>
       <c r="C2" t="n">
-        <v>14860</v>
+        <v>10423</v>
       </c>
       <c r="D2" t="n">
-        <v>12671</v>
+        <v>13440</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2191</v>
+        <v>2660</v>
       </c>
       <c r="C3" t="n">
-        <v>3537</v>
+        <v>2507</v>
       </c>
       <c r="D3" t="n">
-        <v>12764</v>
+        <v>15173</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2465</v>
+        <v>2894</v>
       </c>
       <c r="C4" t="n">
-        <v>4833</v>
+        <v>3956</v>
       </c>
       <c r="D4" t="n">
-        <v>10934</v>
+        <v>14776</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2324</v>
+        <v>2614</v>
       </c>
       <c r="C5" t="n">
-        <v>6627</v>
+        <v>5729</v>
       </c>
       <c r="D5" t="n">
-        <v>6133</v>
+        <v>7851</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1509</v>
+        <v>1629</v>
       </c>
       <c r="C6" t="n">
-        <v>7680</v>
+        <v>6710</v>
       </c>
       <c r="D6" t="n">
-        <v>2435</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="C7" t="n">
-        <v>6130</v>
+        <v>5519</v>
       </c>
       <c r="D7" t="n">
-        <v>884</v>
+        <v>895</v>
       </c>
     </row>
     <row r="8">
@@ -3666,10 +3666,10 @@
         <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>3236</v>
+        <v>3019</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1150</v>
+        <v>1102</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5535</v>
+        <v>5419</v>
       </c>
       <c r="C2" t="n">
-        <v>5229</v>
+        <v>6496</v>
       </c>
       <c r="D2" t="n">
-        <v>11808</v>
+        <v>8438</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2753</v>
+        <v>3676</v>
       </c>
       <c r="C2" t="n">
-        <v>8559</v>
+        <v>6003</v>
       </c>
       <c r="D2" t="n">
-        <v>9427</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2969</v>
+        <v>3610</v>
       </c>
       <c r="C3" t="n">
-        <v>6384</v>
+        <v>4500</v>
       </c>
       <c r="D3" t="n">
-        <v>13697</v>
+        <v>16311</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3406</v>
+        <v>3895</v>
       </c>
       <c r="C4" t="n">
-        <v>7078</v>
+        <v>5853</v>
       </c>
       <c r="D4" t="n">
-        <v>11233</v>
+        <v>15076</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1437</v>
+        <v>1553</v>
       </c>
       <c r="C5" t="n">
-        <v>10358</v>
+        <v>9011</v>
       </c>
       <c r="D5" t="n">
-        <v>5608</v>
+        <v>7004</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="C6" t="n">
-        <v>7437</v>
+        <v>6658</v>
       </c>
       <c r="D6" t="n">
-        <v>1946</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="7">
@@ -4274,10 +4274,10 @@
         <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>3171</v>
+        <v>2958</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>542</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1127</v>
+        <v>1079</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6831</v>
+        <v>7293</v>
       </c>
       <c r="C2" t="n">
-        <v>5198</v>
+        <v>4372</v>
       </c>
       <c r="D2" t="n">
-        <v>14525</v>
+        <v>12774</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2352</v>
+        <v>2303</v>
       </c>
       <c r="C3" t="n">
-        <v>2635</v>
+        <v>3273</v>
       </c>
       <c r="D3" t="n">
-        <v>2623</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4557,7 +4557,7 @@
         <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4496</v>
+        <v>4873</v>
       </c>
       <c r="C2" t="n">
-        <v>9403</v>
+        <v>7499</v>
       </c>
       <c r="D2" t="n">
-        <v>25341</v>
+        <v>15354</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3768</v>
+        <v>3937</v>
       </c>
       <c r="C3" t="n">
-        <v>3564</v>
+        <v>3393</v>
       </c>
       <c r="D3" t="n">
-        <v>4429</v>
+        <v>3705</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1055</v>
+        <v>1034</v>
       </c>
       <c r="C4" t="n">
-        <v>1587</v>
+        <v>1960</v>
       </c>
       <c r="D4" t="n">
-        <v>1709</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
         <v>864</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4571</v>
+        <v>4870</v>
       </c>
       <c r="C2" t="n">
-        <v>6605</v>
+        <v>9012</v>
       </c>
       <c r="D2" t="n">
-        <v>23574</v>
+        <v>28913</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3399</v>
+        <v>3620</v>
       </c>
       <c r="C3" t="n">
-        <v>5841</v>
+        <v>4875</v>
       </c>
       <c r="D3" t="n">
-        <v>7456</v>
+        <v>5302</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2040</v>
+        <v>2101</v>
       </c>
       <c r="C4" t="n">
-        <v>2673</v>
+        <v>2730</v>
       </c>
       <c r="D4" t="n">
-        <v>2179</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="C5" t="n">
-        <v>963</v>
+        <v>1165</v>
       </c>
       <c r="D5" t="n">
-        <v>1233</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
         <v>910</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5351</v>
+        <v>6376</v>
       </c>
       <c r="C2" t="n">
-        <v>9153</v>
+        <v>10363</v>
       </c>
       <c r="D2" t="n">
-        <v>24182</v>
+        <v>29618</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3253</v>
+        <v>3465</v>
       </c>
       <c r="C3" t="n">
-        <v>5426</v>
+        <v>6096</v>
       </c>
       <c r="D3" t="n">
-        <v>9381</v>
+        <v>8517</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2317</v>
+        <v>2434</v>
       </c>
       <c r="C4" t="n">
-        <v>4294</v>
+        <v>3800</v>
       </c>
       <c r="D4" t="n">
-        <v>3075</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1037</v>
+        <v>1056</v>
       </c>
       <c r="C5" t="n">
-        <v>1845</v>
+        <v>1967</v>
       </c>
       <c r="D5" t="n">
-        <v>1347</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C6" t="n">
-        <v>634</v>
+        <v>738</v>
       </c>
       <c r="D6" t="n">
-        <v>953</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
         <v>659</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
         <v>484</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
         <v>378</v>
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5605,7 +5605,7 @@
         <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7106</v>
+        <v>7530</v>
       </c>
       <c r="C2" t="n">
-        <v>10734</v>
+        <v>6523</v>
       </c>
       <c r="D2" t="n">
-        <v>31468</v>
+        <v>38161</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3102</v>
+        <v>3538</v>
       </c>
       <c r="C3" t="n">
-        <v>6005</v>
+        <v>6780</v>
       </c>
       <c r="D3" t="n">
-        <v>10321</v>
+        <v>10465</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1718</v>
+        <v>1819</v>
       </c>
       <c r="C4" t="n">
-        <v>3996</v>
+        <v>4149</v>
       </c>
       <c r="D4" t="n">
-        <v>3605</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>879</v>
+        <v>913</v>
       </c>
       <c r="C5" t="n">
-        <v>2298</v>
+        <v>2118</v>
       </c>
       <c r="D5" t="n">
-        <v>1289</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C6" t="n">
-        <v>838</v>
+        <v>914</v>
       </c>
       <c r="D6" t="n">
-        <v>776</v>
+        <v>766</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="D7" t="n">
         <v>513</v>
@@ -5843,7 +5843,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
         <v>364</v>
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
         <v>270</v>
@@ -5868,7 +5868,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
         <v>151</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>194</v>
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6593</v>
+        <v>5749</v>
       </c>
       <c r="C2" t="n">
-        <v>9826</v>
+        <v>5931</v>
       </c>
       <c r="D2" t="n">
-        <v>23378</v>
+        <v>45473</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4255</v>
+        <v>4609</v>
       </c>
       <c r="C3" t="n">
-        <v>7542</v>
+        <v>5695</v>
       </c>
       <c r="D3" t="n">
-        <v>13114</v>
+        <v>14347</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2117</v>
+        <v>2357</v>
       </c>
       <c r="C4" t="n">
-        <v>5127</v>
+        <v>5653</v>
       </c>
       <c r="D4" t="n">
-        <v>4814</v>
+        <v>4441</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1160</v>
+        <v>1220</v>
       </c>
       <c r="C5" t="n">
-        <v>3244</v>
+        <v>3263</v>
       </c>
       <c r="D5" t="n">
-        <v>1716</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>545</v>
+        <v>562</v>
       </c>
       <c r="C6" t="n">
-        <v>1646</v>
+        <v>1584</v>
       </c>
       <c r="D6" t="n">
-        <v>863</v>
+        <v>833</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>610</v>
+        <v>658</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -6154,7 +6154,7 @@
         <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="D8" t="n">
         <v>388</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
         <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6238,7 +6238,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4806</v>
+        <v>6098</v>
       </c>
       <c r="C2" t="n">
-        <v>8078</v>
+        <v>6614</v>
       </c>
       <c r="D2" t="n">
-        <v>19661</v>
+        <v>46372</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4433</v>
+        <v>4295</v>
       </c>
       <c r="C3" t="n">
-        <v>7606</v>
+        <v>5048</v>
       </c>
       <c r="D3" t="n">
-        <v>13812</v>
+        <v>18294</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2732</v>
+        <v>2949</v>
       </c>
       <c r="C4" t="n">
-        <v>6388</v>
+        <v>5558</v>
       </c>
       <c r="D4" t="n">
-        <v>6261</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1426</v>
+        <v>1563</v>
       </c>
       <c r="C5" t="n">
-        <v>4206</v>
+        <v>4448</v>
       </c>
       <c r="D5" t="n">
-        <v>2212</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>775</v>
+        <v>798</v>
       </c>
       <c r="C6" t="n">
-        <v>2470</v>
+        <v>2452</v>
       </c>
       <c r="D6" t="n">
-        <v>1006</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C7" t="n">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>443</v>
+        <v>470</v>
       </c>
       <c r="D8" t="n">
         <v>407</v>
@@ -6479,10 +6479,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>157</v>
@@ -6532,7 +6532,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
         <v>90</v>
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>

--- a/output/yearly_population_iteration_5_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_5_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7188</v>
+        <v>1168</v>
       </c>
       <c r="C2" t="n">
-        <v>9716</v>
+        <v>2204</v>
       </c>
       <c r="D2" t="n">
-        <v>37610</v>
+        <v>13600</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4195</v>
+        <v>2050</v>
       </c>
       <c r="C3" t="n">
-        <v>5081</v>
+        <v>7628</v>
       </c>
       <c r="D3" t="n">
-        <v>21078</v>
+        <v>11518</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3042</v>
+        <v>1311</v>
       </c>
       <c r="C4" t="n">
-        <v>5129</v>
+        <v>11223</v>
       </c>
       <c r="D4" t="n">
-        <v>8047</v>
+        <v>5355</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1918</v>
+        <v>602</v>
       </c>
       <c r="C5" t="n">
-        <v>4909</v>
+        <v>6731</v>
       </c>
       <c r="D5" t="n">
-        <v>2659</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1048</v>
+        <v>240</v>
       </c>
       <c r="C6" t="n">
-        <v>3360</v>
+        <v>2520</v>
       </c>
       <c r="D6" t="n">
-        <v>1103</v>
+        <v>740</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>478</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>1768</v>
+        <v>913</v>
       </c>
       <c r="D7" t="n">
-        <v>636</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>777</v>
+        <v>368</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8758</v>
+        <v>1232</v>
       </c>
       <c r="C2" t="n">
-        <v>5889</v>
+        <v>3078</v>
       </c>
       <c r="D2" t="n">
-        <v>30774</v>
+        <v>13981</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4502</v>
+        <v>1390</v>
       </c>
       <c r="C3" t="n">
-        <v>6296</v>
+        <v>4282</v>
       </c>
       <c r="D3" t="n">
-        <v>21909</v>
+        <v>11134</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3010</v>
+        <v>1433</v>
       </c>
       <c r="C4" t="n">
-        <v>4999</v>
+        <v>9091</v>
       </c>
       <c r="D4" t="n">
-        <v>9929</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2109</v>
+        <v>808</v>
       </c>
       <c r="C5" t="n">
-        <v>4859</v>
+        <v>8941</v>
       </c>
       <c r="D5" t="n">
-        <v>3380</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1283</v>
+        <v>361</v>
       </c>
       <c r="C6" t="n">
-        <v>4011</v>
+        <v>4539</v>
       </c>
       <c r="D6" t="n">
-        <v>1327</v>
+        <v>917</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>645</v>
+        <v>138</v>
       </c>
       <c r="C7" t="n">
-        <v>2436</v>
+        <v>1661</v>
       </c>
       <c r="D7" t="n">
-        <v>691</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>264</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>1194</v>
+        <v>606</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>513</v>
+        <v>319</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
+        <v>238</v>
+      </c>
+      <c r="D10" t="n">
         <v>265</v>
-      </c>
-      <c r="D10" t="n">
-        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8887</v>
+        <v>673</v>
       </c>
       <c r="C2" t="n">
-        <v>7742</v>
+        <v>1349</v>
       </c>
       <c r="D2" t="n">
-        <v>33889</v>
+        <v>9528</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5008</v>
+        <v>1298</v>
       </c>
       <c r="C3" t="n">
-        <v>5457</v>
+        <v>3681</v>
       </c>
       <c r="D3" t="n">
-        <v>21570</v>
+        <v>11190</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3060</v>
+        <v>1549</v>
       </c>
       <c r="C4" t="n">
-        <v>5394</v>
+        <v>8020</v>
       </c>
       <c r="D4" t="n">
-        <v>11256</v>
+        <v>6834</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2209</v>
+        <v>796</v>
       </c>
       <c r="C5" t="n">
-        <v>4769</v>
+        <v>10168</v>
       </c>
       <c r="D5" t="n">
-        <v>4220</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1456</v>
+        <v>284</v>
       </c>
       <c r="C6" t="n">
-        <v>4317</v>
+        <v>5603</v>
       </c>
       <c r="D6" t="n">
-        <v>1572</v>
+        <v>931</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>796</v>
+        <v>69</v>
       </c>
       <c r="C7" t="n">
-        <v>3028</v>
+        <v>1547</v>
       </c>
       <c r="D7" t="n">
-        <v>771</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>359</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1656</v>
+        <v>514</v>
       </c>
       <c r="D8" t="n">
-        <v>477</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>766</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
-        <v>335</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>349</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>207</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8270</v>
+        <v>1069</v>
       </c>
       <c r="C2" t="n">
-        <v>5326</v>
+        <v>2713</v>
       </c>
       <c r="D2" t="n">
-        <v>28146</v>
+        <v>9290</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5721</v>
+        <v>878</v>
       </c>
       <c r="C3" t="n">
-        <v>8384</v>
+        <v>2243</v>
       </c>
       <c r="D3" t="n">
-        <v>23129</v>
+        <v>10180</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2041</v>
+        <v>1282</v>
       </c>
       <c r="C4" t="n">
-        <v>7478</v>
+        <v>5722</v>
       </c>
       <c r="D4" t="n">
-        <v>10264</v>
+        <v>7378</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1345</v>
+        <v>986</v>
       </c>
       <c r="C5" t="n">
-        <v>4230</v>
+        <v>9023</v>
       </c>
       <c r="D5" t="n">
-        <v>2674</v>
+        <v>3305</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>735</v>
+        <v>436</v>
       </c>
       <c r="C6" t="n">
-        <v>2967</v>
+        <v>7717</v>
       </c>
       <c r="D6" t="n">
-        <v>755</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>331</v>
+        <v>124</v>
       </c>
       <c r="C7" t="n">
-        <v>1622</v>
+        <v>3270</v>
       </c>
       <c r="D7" t="n">
-        <v>467</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>750</v>
+        <v>933</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
+        <v>69</v>
+      </c>
+      <c r="D14" t="n">
         <v>67</v>
-      </c>
-      <c r="D14" t="n">
-        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
+        <v>66</v>
+      </c>
+      <c r="D15" t="n">
         <v>49</v>
-      </c>
-      <c r="D15" t="n">
-        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5017</v>
+        <v>597</v>
       </c>
       <c r="C2" t="n">
-        <v>2486</v>
+        <v>2869</v>
       </c>
       <c r="D2" t="n">
-        <v>20110</v>
+        <v>7265</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5846</v>
+        <v>826</v>
       </c>
       <c r="C3" t="n">
-        <v>6396</v>
+        <v>2226</v>
       </c>
       <c r="D3" t="n">
-        <v>22701</v>
+        <v>9496</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2930</v>
+        <v>1055</v>
       </c>
       <c r="C4" t="n">
-        <v>7946</v>
+        <v>4231</v>
       </c>
       <c r="D4" t="n">
-        <v>11903</v>
+        <v>7628</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1498</v>
+        <v>1049</v>
       </c>
       <c r="C5" t="n">
-        <v>5654</v>
+        <v>7882</v>
       </c>
       <c r="D5" t="n">
-        <v>3616</v>
+        <v>3776</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>877</v>
+        <v>543</v>
       </c>
       <c r="C6" t="n">
-        <v>3543</v>
+        <v>8476</v>
       </c>
       <c r="D6" t="n">
-        <v>933</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>309</v>
+        <v>131</v>
       </c>
       <c r="C7" t="n">
-        <v>2120</v>
+        <v>4713</v>
       </c>
       <c r="D7" t="n">
-        <v>507</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>994</v>
+        <v>1465</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>387</v>
+        <v>427</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5538</v>
+        <v>476</v>
       </c>
       <c r="C2" t="n">
-        <v>5699</v>
+        <v>13782</v>
       </c>
       <c r="D2" t="n">
-        <v>21600</v>
+        <v>17542</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4624</v>
+        <v>620</v>
       </c>
       <c r="C3" t="n">
-        <v>4084</v>
+        <v>2235</v>
       </c>
       <c r="D3" t="n">
-        <v>20823</v>
+        <v>8587</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3589</v>
+        <v>840</v>
       </c>
       <c r="C4" t="n">
-        <v>7036</v>
+        <v>3219</v>
       </c>
       <c r="D4" t="n">
-        <v>13303</v>
+        <v>7683</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1848</v>
+        <v>972</v>
       </c>
       <c r="C5" t="n">
-        <v>6592</v>
+        <v>6105</v>
       </c>
       <c r="D5" t="n">
-        <v>4778</v>
+        <v>4179</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1035</v>
+        <v>675</v>
       </c>
       <c r="C6" t="n">
-        <v>4475</v>
+        <v>8230</v>
       </c>
       <c r="D6" t="n">
-        <v>1307</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>464</v>
+        <v>242</v>
       </c>
       <c r="C7" t="n">
-        <v>2739</v>
+        <v>6223</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>756</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>1444</v>
+        <v>2720</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>491</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>610</v>
+        <v>797</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3316</v>
+        <v>327</v>
       </c>
       <c r="C2" t="n">
-        <v>2709</v>
+        <v>7497</v>
       </c>
       <c r="D2" t="n">
-        <v>15045</v>
+        <v>12770</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4668</v>
+        <v>832</v>
       </c>
       <c r="C3" t="n">
-        <v>4496</v>
+        <v>5373</v>
       </c>
       <c r="D3" t="n">
-        <v>20437</v>
+        <v>9949</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3928</v>
+        <v>1318</v>
       </c>
       <c r="C4" t="n">
-        <v>6629</v>
+        <v>5090</v>
       </c>
       <c r="D4" t="n">
-        <v>14232</v>
+        <v>7895</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1894</v>
+        <v>668</v>
       </c>
       <c r="C5" t="n">
-        <v>7693</v>
+        <v>10371</v>
       </c>
       <c r="D5" t="n">
-        <v>5065</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>839</v>
+        <v>223</v>
       </c>
       <c r="C6" t="n">
-        <v>5324</v>
+        <v>7953</v>
       </c>
       <c r="D6" t="n">
-        <v>1277</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="C7" t="n">
-        <v>2789</v>
+        <v>2665</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>1022</v>
+        <v>781</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4255</v>
+        <v>216</v>
       </c>
       <c r="C2" t="n">
-        <v>3916</v>
+        <v>3820</v>
       </c>
       <c r="D2" t="n">
-        <v>13520</v>
+        <v>8843</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3526</v>
+        <v>529</v>
       </c>
       <c r="C3" t="n">
-        <v>3306</v>
+        <v>5689</v>
       </c>
       <c r="D3" t="n">
-        <v>18526</v>
+        <v>9735</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3686</v>
+        <v>921</v>
       </c>
       <c r="C4" t="n">
-        <v>5508</v>
+        <v>4912</v>
       </c>
       <c r="D4" t="n">
-        <v>14752</v>
+        <v>7656</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2378</v>
+        <v>648</v>
       </c>
       <c r="C5" t="n">
-        <v>7136</v>
+        <v>7057</v>
       </c>
       <c r="D5" t="n">
-        <v>6231</v>
+        <v>3934</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1116</v>
+        <v>227</v>
       </c>
       <c r="C6" t="n">
-        <v>6306</v>
+        <v>7372</v>
       </c>
       <c r="D6" t="n">
-        <v>1769</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>305</v>
+        <v>51</v>
       </c>
       <c r="C7" t="n">
-        <v>3836</v>
+        <v>3518</v>
       </c>
       <c r="D7" t="n">
-        <v>654</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1665</v>
+        <v>935</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>517</v>
+        <v>271</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>121</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2905</v>
+        <v>416</v>
       </c>
       <c r="C2" t="n">
-        <v>2208</v>
+        <v>10191</v>
       </c>
       <c r="D2" t="n">
-        <v>10198</v>
+        <v>10801</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3294</v>
+        <v>320</v>
       </c>
       <c r="C3" t="n">
-        <v>3219</v>
+        <v>4090</v>
       </c>
       <c r="D3" t="n">
-        <v>17095</v>
+        <v>8914</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3350</v>
+        <v>651</v>
       </c>
       <c r="C4" t="n">
-        <v>4664</v>
+        <v>5235</v>
       </c>
       <c r="D4" t="n">
-        <v>14916</v>
+        <v>7802</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2624</v>
+        <v>698</v>
       </c>
       <c r="C5" t="n">
-        <v>6683</v>
+        <v>5845</v>
       </c>
       <c r="D5" t="n">
-        <v>7001</v>
+        <v>4457</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1320</v>
+        <v>375</v>
       </c>
       <c r="C6" t="n">
-        <v>6820</v>
+        <v>7135</v>
       </c>
       <c r="D6" t="n">
-        <v>2185</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>273</v>
+        <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>4678</v>
+        <v>5439</v>
       </c>
       <c r="D7" t="n">
-        <v>732</v>
+        <v>707</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>2155</v>
+        <v>2133</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>591</v>
+        <v>559</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5086</v>
+        <v>307</v>
       </c>
       <c r="C2" t="n">
-        <v>10423</v>
+        <v>11883</v>
       </c>
       <c r="D2" t="n">
-        <v>13440</v>
+        <v>18523</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2660</v>
+        <v>298</v>
       </c>
       <c r="C3" t="n">
-        <v>2507</v>
+        <v>6124</v>
       </c>
       <c r="D3" t="n">
-        <v>15173</v>
+        <v>8572</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2894</v>
+        <v>444</v>
       </c>
       <c r="C4" t="n">
-        <v>3956</v>
+        <v>4554</v>
       </c>
       <c r="D4" t="n">
-        <v>14776</v>
+        <v>7756</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2614</v>
+        <v>614</v>
       </c>
       <c r="C5" t="n">
-        <v>5729</v>
+        <v>5430</v>
       </c>
       <c r="D5" t="n">
-        <v>7851</v>
+        <v>4867</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1629</v>
+        <v>472</v>
       </c>
       <c r="C6" t="n">
-        <v>6710</v>
+        <v>6469</v>
       </c>
       <c r="D6" t="n">
-        <v>2758</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>530</v>
+        <v>196</v>
       </c>
       <c r="C7" t="n">
-        <v>5519</v>
+        <v>6148</v>
       </c>
       <c r="D7" t="n">
-        <v>895</v>
+        <v>888</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>3019</v>
+        <v>3590</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1102</v>
+        <v>1222</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5419</v>
+        <v>3084</v>
       </c>
       <c r="C2" t="n">
-        <v>6496</v>
+        <v>17417</v>
       </c>
       <c r="D2" t="n">
-        <v>8438</v>
+        <v>15615</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3676</v>
+        <v>227</v>
       </c>
       <c r="C2" t="n">
-        <v>6003</v>
+        <v>26538</v>
       </c>
       <c r="D2" t="n">
-        <v>10000</v>
+        <v>16427</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3610</v>
+        <v>250</v>
       </c>
       <c r="C3" t="n">
-        <v>4500</v>
+        <v>7642</v>
       </c>
       <c r="D3" t="n">
-        <v>16311</v>
+        <v>9283</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3895</v>
+        <v>337</v>
       </c>
       <c r="C4" t="n">
-        <v>5853</v>
+        <v>5108</v>
       </c>
       <c r="D4" t="n">
-        <v>15076</v>
+        <v>7645</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1553</v>
+        <v>503</v>
       </c>
       <c r="C5" t="n">
-        <v>9011</v>
+        <v>4938</v>
       </c>
       <c r="D5" t="n">
-        <v>7004</v>
+        <v>5088</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C6" t="n">
-        <v>6658</v>
+        <v>5918</v>
       </c>
       <c r="D6" t="n">
-        <v>2114</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>269</v>
       </c>
       <c r="C7" t="n">
-        <v>2958</v>
+        <v>6277</v>
       </c>
       <c r="D7" t="n">
-        <v>542</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>1079</v>
+        <v>4556</v>
       </c>
       <c r="D8" t="n">
-        <v>293</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>322</v>
+        <v>2126</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>655</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7293</v>
+        <v>5063</v>
       </c>
       <c r="C2" t="n">
-        <v>4372</v>
+        <v>8509</v>
       </c>
       <c r="D2" t="n">
-        <v>12774</v>
+        <v>15009</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2303</v>
+        <v>997</v>
       </c>
       <c r="C3" t="n">
-        <v>3273</v>
+        <v>6878</v>
       </c>
       <c r="D3" t="n">
-        <v>2056</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4873</v>
+        <v>2605</v>
       </c>
       <c r="C2" t="n">
-        <v>7499</v>
+        <v>6810</v>
       </c>
       <c r="D2" t="n">
-        <v>15354</v>
+        <v>17377</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3937</v>
+        <v>2577</v>
       </c>
       <c r="C3" t="n">
-        <v>3393</v>
+        <v>6801</v>
       </c>
       <c r="D3" t="n">
-        <v>3705</v>
+        <v>4693</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1034</v>
+        <v>488</v>
       </c>
       <c r="C4" t="n">
-        <v>1960</v>
+        <v>4274</v>
       </c>
       <c r="D4" t="n">
-        <v>1595</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>112</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4870</v>
+        <v>2554</v>
       </c>
       <c r="C2" t="n">
-        <v>9012</v>
+        <v>13273</v>
       </c>
       <c r="D2" t="n">
-        <v>28913</v>
+        <v>18265</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3620</v>
+        <v>2138</v>
       </c>
       <c r="C3" t="n">
-        <v>4875</v>
+        <v>5858</v>
       </c>
       <c r="D3" t="n">
-        <v>5302</v>
+        <v>6478</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2101</v>
+        <v>1327</v>
       </c>
       <c r="C4" t="n">
-        <v>2730</v>
+        <v>5689</v>
       </c>
       <c r="D4" t="n">
-        <v>1951</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>485</v>
+        <v>255</v>
       </c>
       <c r="C5" t="n">
-        <v>1165</v>
+        <v>2546</v>
       </c>
       <c r="D5" t="n">
-        <v>1213</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6376</v>
+        <v>2101</v>
       </c>
       <c r="C2" t="n">
-        <v>10363</v>
+        <v>13561</v>
       </c>
       <c r="D2" t="n">
-        <v>29618</v>
+        <v>19724</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3465</v>
+        <v>1930</v>
       </c>
       <c r="C3" t="n">
-        <v>6096</v>
+        <v>8520</v>
       </c>
       <c r="D3" t="n">
-        <v>8517</v>
+        <v>7897</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2434</v>
+        <v>1491</v>
       </c>
       <c r="C4" t="n">
-        <v>3800</v>
+        <v>5610</v>
       </c>
       <c r="D4" t="n">
-        <v>2502</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1056</v>
+        <v>660</v>
       </c>
       <c r="C5" t="n">
-        <v>1967</v>
+        <v>4212</v>
       </c>
       <c r="D5" t="n">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>275</v>
+        <v>163</v>
       </c>
       <c r="C6" t="n">
-        <v>738</v>
+        <v>1465</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>832</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7530</v>
+        <v>2794</v>
       </c>
       <c r="C2" t="n">
-        <v>6523</v>
+        <v>7956</v>
       </c>
       <c r="D2" t="n">
-        <v>38161</v>
+        <v>21471</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3538</v>
+        <v>1661</v>
       </c>
       <c r="C3" t="n">
-        <v>6780</v>
+        <v>9647</v>
       </c>
       <c r="D3" t="n">
-        <v>10465</v>
+        <v>9138</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1819</v>
+        <v>1467</v>
       </c>
       <c r="C4" t="n">
-        <v>4149</v>
+        <v>7029</v>
       </c>
       <c r="D4" t="n">
-        <v>3075</v>
+        <v>3785</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C5" t="n">
-        <v>2118</v>
+        <v>4835</v>
       </c>
       <c r="D5" t="n">
-        <v>1174</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>311</v>
+        <v>344</v>
       </c>
       <c r="C6" t="n">
-        <v>914</v>
+        <v>2794</v>
       </c>
       <c r="D6" t="n">
-        <v>766</v>
+        <v>887</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="C7" t="n">
-        <v>343</v>
+        <v>853</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5749</v>
+        <v>2537</v>
       </c>
       <c r="C2" t="n">
-        <v>5931</v>
+        <v>8019</v>
       </c>
       <c r="D2" t="n">
-        <v>45473</v>
+        <v>22865</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4609</v>
+        <v>1759</v>
       </c>
       <c r="C3" t="n">
-        <v>5695</v>
+        <v>7783</v>
       </c>
       <c r="D3" t="n">
-        <v>14347</v>
+        <v>10201</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2357</v>
+        <v>1331</v>
       </c>
       <c r="C4" t="n">
-        <v>5653</v>
+        <v>8164</v>
       </c>
       <c r="D4" t="n">
-        <v>4441</v>
+        <v>4507</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1220</v>
+        <v>1026</v>
       </c>
       <c r="C5" t="n">
-        <v>3263</v>
+        <v>5720</v>
       </c>
       <c r="D5" t="n">
-        <v>1521</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>562</v>
+        <v>525</v>
       </c>
       <c r="C6" t="n">
-        <v>1584</v>
+        <v>3706</v>
       </c>
       <c r="D6" t="n">
-        <v>833</v>
+        <v>967</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C7" t="n">
-        <v>658</v>
+        <v>1727</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>289</v>
+        <v>535</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6098</v>
+        <v>2344</v>
       </c>
       <c r="C2" t="n">
-        <v>6614</v>
+        <v>5132</v>
       </c>
       <c r="D2" t="n">
-        <v>46372</v>
+        <v>18219</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4295</v>
+        <v>2317</v>
       </c>
       <c r="C3" t="n">
-        <v>5048</v>
+        <v>11654</v>
       </c>
       <c r="D3" t="n">
-        <v>18294</v>
+        <v>11163</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2949</v>
+        <v>948</v>
       </c>
       <c r="C4" t="n">
-        <v>5558</v>
+        <v>10428</v>
       </c>
       <c r="D4" t="n">
-        <v>6207</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1563</v>
+        <v>485</v>
       </c>
       <c r="C5" t="n">
-        <v>4448</v>
+        <v>3631</v>
       </c>
       <c r="D5" t="n">
-        <v>1992</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>798</v>
+        <v>176</v>
       </c>
       <c r="C6" t="n">
-        <v>2452</v>
+        <v>1692</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>641</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>1138</v>
+        <v>524</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>452</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>470</v>
+        <v>279</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
         <v>202</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
